--- a/database/ld.xlsx
+++ b/database/ld.xlsx
@@ -23,12 +23,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
   <si>
     <t xml:space="preserve">Test2017-2018.xlsx</t>
   </si>
   <si>
-    <t xml:space="preserve">Patients</t>
+    <t xml:space="preserve">Society Maintanence Charges</t>
   </si>
   <si>
     <t xml:space="preserve">LEDGER</t>
@@ -64,6 +64,27 @@
     <t xml:space="preserve">Balance</t>
   </si>
   <si>
+    <t xml:space="preserve">SocMc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apt A101 – Apr 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apt B101 – Apr 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apt C101 – Apr 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apt D101 – Apr 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SocInt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apt E101 – Apr 2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">Inc.Exp.A/c</t>
   </si>
   <si>
@@ -79,11 +100,12 @@
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -105,6 +127,13 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -151,7 +180,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -177,6 +206,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -234,20 +271,6 @@
           <cell r="A8">
             <v>42482</v>
           </cell>
-          <cell r="B8" t="str">
-            <v>Patients</v>
-          </cell>
-          <cell r="C8" t="str">
-            <v>CMS/ LIPL PMT APR16 - C1</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="G8">
-            <v>0</v>
-          </cell>
-          <cell r="H8">
-            <v>400</v>
-          </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
@@ -255,38 +278,10 @@
           <cell r="A7">
             <v>42496</v>
           </cell>
-          <cell r="B7" t="str">
-            <v>Patients</v>
-          </cell>
-          <cell r="C7" t="str">
-            <v>CMS/ DOCTOR PAID BY LYBRATE</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="G7">
-            <v>0</v>
-          </cell>
-          <cell r="H7">
-            <v>600</v>
-          </cell>
         </row>
         <row r="8">
           <cell r="A8">
             <v>42513</v>
-          </cell>
-          <cell r="B8" t="str">
-            <v>Patients</v>
-          </cell>
-          <cell r="C8" t="str">
-            <v>CMS/ DOCTOR PAID BY LYBRATE</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="G8">
-            <v>0</v>
-          </cell>
-          <cell r="H8">
-            <v>1100</v>
           </cell>
         </row>
       </sheetData>
@@ -298,40 +293,12 @@
           <cell r="A7">
             <v>42632</v>
           </cell>
-          <cell r="B7" t="str">
-            <v>Patients</v>
-          </cell>
-          <cell r="C7" t="str">
-            <v>SCB/401494/SCB -Intas</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="G7">
-            <v>0</v>
-          </cell>
-          <cell r="H7">
-            <v>10000</v>
-          </cell>
         </row>
       </sheetData>
       <sheetData sheetId="6">
         <row r="7">
           <cell r="A7">
             <v>42671</v>
-          </cell>
-          <cell r="B7" t="str">
-            <v>Patients</v>
-          </cell>
-          <cell r="C7" t="str">
-            <v>SHRI MARUTINANDAN HEALTHCARE/</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="G7">
-            <v>0</v>
-          </cell>
-          <cell r="H7">
-            <v>41600</v>
           </cell>
         </row>
       </sheetData>
@@ -373,7 +340,7 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="33.77"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="8.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="3" width="9.48"/>
@@ -3503,134 +3470,119 @@
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="n">
         <f aca="false">[1]Apr!A8</f>
         <v>42482</v>
       </c>
-      <c r="B6" s="1" t="str">
-        <f aca="false">[1]Apr!B8</f>
-        <v>Patients</v>
-      </c>
-      <c r="C6" s="1" t="str">
-        <f aca="false">[1]Apr!C8</f>
-        <v>CMS/ LIPL PMT APR16 - C1</v>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="3" t="n">
-        <f aca="false">SUM([1]Apr!G8:H8)</f>
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="H6" s="3" t="n">
         <f aca="false">Pt!H5+F6-E6</f>
-        <v>400</v>
+        <v>1200</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="n">
         <f aca="false">[1]May!A7</f>
         <v>42496</v>
       </c>
-      <c r="B7" s="1" t="str">
-        <f aca="false">[1]May!B7</f>
-        <v>Patients</v>
-      </c>
-      <c r="C7" s="1" t="str">
-        <f aca="false">[1]May!C7</f>
-        <v>CMS/ DOCTOR PAID BY LYBRATE</v>
+      <c r="B7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="3" t="n">
-        <f aca="false">SUM([1]May!G7:H7)</f>
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="H7" s="3" t="n">
         <f aca="false">Pt!H6+F7-E7</f>
-        <v>1000</v>
+        <v>2400</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="n">
         <f aca="false">[1]May!A8</f>
         <v>42513</v>
       </c>
-      <c r="B8" s="1" t="str">
-        <f aca="false">[1]May!B8</f>
-        <v>Patients</v>
-      </c>
-      <c r="C8" s="1" t="str">
-        <f aca="false">[1]May!C8</f>
-        <v>CMS/ DOCTOR PAID BY LYBRATE</v>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="3" t="n">
-        <f aca="false">SUM([1]May!G8:H8)</f>
-        <v>1100</v>
+        <v>2400</v>
       </c>
       <c r="H8" s="3" t="n">
         <f aca="false">Pt!H7+F8-E8</f>
-        <v>2100</v>
+        <v>4800</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="n">
         <f aca="false">[1]Sep!A7</f>
         <v>42632</v>
       </c>
-      <c r="B9" s="1" t="str">
-        <f aca="false">[1]Sep!B7</f>
-        <v>Patients</v>
-      </c>
-      <c r="C9" s="1" t="str">
-        <f aca="false">[1]Sep!C7</f>
-        <v>SCB/401494/SCB -Intas</v>
+      <c r="B9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="3" t="n">
-        <f aca="false">SUM([1]Sep!G7:H7)</f>
-        <v>10000</v>
+        <v>2400</v>
       </c>
       <c r="H9" s="3" t="n">
         <f aca="false">Pt!H8+F9-E9</f>
-        <v>12100</v>
+        <v>7200</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="n">
         <f aca="false">[1]Oct!A7</f>
         <v>42671</v>
       </c>
-      <c r="B10" s="1" t="str">
-        <f aca="false">[1]Oct!B7</f>
-        <v>Patients</v>
-      </c>
-      <c r="C10" s="1" t="str">
-        <f aca="false">[1]Oct!C7</f>
-        <v>SHRI MARUTINANDAN HEALTHCARE/</v>
+      <c r="B10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="3" t="n">
-        <f aca="false">SUM([1]Oct!G7:H7)</f>
-        <v>41600</v>
+        <v>450</v>
       </c>
       <c r="H10" s="3" t="n">
         <f aca="false">Pt!H9+F10-E10</f>
-        <v>53700</v>
+        <v>7650</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3638,17 +3590,17 @@
         <v>42825</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>16</v>
       </c>
       <c r="E11" s="3" t="n">
         <f aca="false">Pt!H10</f>
-        <v>53700</v>
+        <v>7650</v>
       </c>
       <c r="H11" s="3" t="n">
         <f aca="false">Pt!H10+F11-E11</f>

--- a/database/ld.xlsx
+++ b/database/ld.xlsx
@@ -5,13 +5,14 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Pt" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="SocMc" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Inst" sheetId="2" state="visible" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="31">
   <si>
     <t xml:space="preserve">Test2017-2018.xlsx</t>
   </si>
@@ -90,17 +91,45 @@
   <si>
     <t xml:space="preserve">C/F</t>
   </si>
+  <si>
+    <t xml:space="preserve">CB2025-2026.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instruments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">By Balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B/F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depreciation @ 7.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depreciation @ 15%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAs</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="167" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -133,6 +162,13 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -180,7 +216,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -215,6 +251,38 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -3489,7 +3557,7 @@
         <v>1200</v>
       </c>
       <c r="H6" s="3" t="n">
-        <f aca="false">Pt!H5+F6-E6</f>
+        <f aca="false">SocMc!H5+F6-E6</f>
         <v>1200</v>
       </c>
     </row>
@@ -3512,7 +3580,7 @@
         <v>1200</v>
       </c>
       <c r="H7" s="3" t="n">
-        <f aca="false">Pt!H6+F7-E7</f>
+        <f aca="false">SocMc!H6+F7-E7</f>
         <v>2400</v>
       </c>
     </row>
@@ -3535,7 +3603,7 @@
         <v>2400</v>
       </c>
       <c r="H8" s="3" t="n">
-        <f aca="false">Pt!H7+F8-E8</f>
+        <f aca="false">SocMc!H7+F8-E8</f>
         <v>4800</v>
       </c>
     </row>
@@ -3558,7 +3626,7 @@
         <v>2400</v>
       </c>
       <c r="H9" s="3" t="n">
-        <f aca="false">Pt!H8+F9-E9</f>
+        <f aca="false">SocMc!H8+F9-E9</f>
         <v>7200</v>
       </c>
     </row>
@@ -3581,7 +3649,7 @@
         <v>450</v>
       </c>
       <c r="H10" s="3" t="n">
-        <f aca="false">Pt!H9+F10-E10</f>
+        <f aca="false">SocMc!H9+F10-E10</f>
         <v>7650</v>
       </c>
     </row>
@@ -3599,11 +3667,11 @@
         <v>16</v>
       </c>
       <c r="E11" s="3" t="n">
-        <f aca="false">Pt!H10</f>
+        <f aca="false">SocMc!H10</f>
         <v>7650</v>
       </c>
       <c r="H11" s="3" t="n">
-        <f aca="false">Pt!H10+F11-E11</f>
+        <f aca="false">SocMc!H10+F11-E11</f>
         <v>0</v>
       </c>
     </row>
@@ -3616,4 +3684,227 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="16.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="9" width="18.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="10" width="8.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="11" width="8.42"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="6" style="11" width="8.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="11" width="8.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="11" width="9.57"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="12"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="12"/>
+      <c r="E2" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15" t="n">
+        <v>44652</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>1359.43</v>
+      </c>
+      <c r="H6" s="11" t="n">
+        <f aca="false">Inst!H5-F6+E6</f>
+        <v>1359.43</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="16" t="n">
+        <v>44653</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <f aca="false">Inst!H6-F7+E7</f>
+        <v>1359.43</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="15" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <f aca="false">(Inst!H7-Inst!H7)*0.075</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="11" t="n">
+        <f aca="false">Inst!H7-F8+E8</f>
+        <v>1359.43</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="15" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <f aca="false">H8*0.15</f>
+        <v>203.9145</v>
+      </c>
+      <c r="H9" s="11" t="n">
+        <f aca="false">Inst!H8-F9+E9</f>
+        <v>1155.5155</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="15" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <f aca="false">H9</f>
+        <v>1155.5155</v>
+      </c>
+      <c r="H10" s="11" t="n">
+        <f aca="false">Inst!H9-F10+E10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="36.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="27" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="28" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/database/ld.xlsx
+++ b/database/ld.xlsx
@@ -10,9 +10,14 @@
   <sheets>
     <sheet name="SocMc" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="Inst" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Dep" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="InExp" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="CapAc" sheetId="5" state="visible" r:id="rId6"/>
+    <sheet name="Bal" sheetId="6" state="visible" r:id="rId7"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
   </externalReferences>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -24,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="90">
   <si>
     <t xml:space="preserve">Test2017-2018.xlsx</t>
   </si>
@@ -117,6 +122,183 @@
   </si>
   <si>
     <t xml:space="preserve">MAs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depreciation Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LD F No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instruments @ 7.5 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instruments @ 15 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Income Expenditure Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Misc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miscellaneous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veh. Exp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle Expenditure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patients</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Med.Cons.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medical Consultation - Freelance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CapAc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expenditure =&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;= Reciepts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profit%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Income from Proffession</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TDStoIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance Sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Movable Assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bank acs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cih</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Anurag Gupta </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAN No:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AFIPG7802B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASST YEAR 2023-2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BALANCE SHEET – PROFESSION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liabilities </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ImAs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immovable Assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CurLb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Liabilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sundry Creditors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CurAs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L&amp;A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loans And Advances</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deposits (Assets)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BkAc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank Accounts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SiH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stock-in-hand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CiH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash-in-hand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MFund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mutual Fund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Furniture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sdr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sundry Debitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total</t>
   </si>
 </sst>
 </file>
@@ -182,12 +364,33 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -216,7 +419,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="39">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -282,6 +485,94 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -396,6 +687,12 @@
       <sheetData sheetId="30"/>
     </sheetDataSet>
   </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </externalLink>
 </file>
 
@@ -3907,4 +4204,1502 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A2:H39"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="1" style="17" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="12"/>
+      <c r="E2" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D5" s="10"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="18" t="e">
+        <f aca="false">[2]Inst!F8</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18" t="e">
+        <f aca="false">H5+E6-F6</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="15" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="18" t="e">
+        <f aca="false">[2]Inst!F9</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18" t="e">
+        <f aca="false">H6+E7-F7</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="15" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18" t="e">
+        <f aca="false">H7</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18" t="e">
+        <f aca="false">H7+E8-F8</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="36.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="27" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="28" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="16.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="9.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="17" width="27.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="10" width="17.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="18" width="10.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="18" width="15.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="18" width="8.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="18" width="10.45"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="12"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="12"/>
+      <c r="E2" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15" t="n">
+        <v>45382</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="E6" s="18" t="e">
+        <f aca="false">[2]Dep!F8</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H6" s="18" t="e">
+        <f aca="false">H5+F6-E6</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="15" t="n">
+        <v>45382</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" s="18" t="e">
+        <f aca="false">[2]Salary!F30</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H7" s="18" t="e">
+        <f aca="false">H6+F7-E7</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="15" t="n">
+        <v>45382</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" s="18" t="e">
+        <f aca="false">[2]misc!F7</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H8" s="18" t="e">
+        <f aca="false">H7+F8-E8</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="15" t="n">
+        <v>45382</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" s="18" t="e">
+        <f aca="false">[2]vehexp!F25</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H9" s="18" t="e">
+        <f aca="false">H8+F9-E9</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="15" t="n">
+        <v>45382</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" s="18" t="e">
+        <f aca="false">[2]Pt!E23</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H10" s="18" t="e">
+        <f aca="false">H9+F10-E10</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="15" t="n">
+        <v>45382</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="18" t="e">
+        <f aca="false">[2]MedCon!E10</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H11" s="18" t="e">
+        <f aca="false">H10+F11-E11</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="15" t="n">
+        <v>45382</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="E12" s="18" t="e">
+        <f aca="false">InExp!H11</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H12" s="18" t="e">
+        <f aca="false">InExp!H11+F12-E12</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D14" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="18" t="e">
+        <f aca="false">SUM(E6:E11)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F14" s="18" t="e">
+        <f aca="false">SUM(F6:F11)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D16" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="20" t="e">
+        <f aca="false">E12/F14</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="36.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="27" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="28" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I39"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="16.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="9.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="17" width="20.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="10" width="18.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="18" width="10.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="18" width="8.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="18" width="10.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="17" width="13.9"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="12"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="12"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="12"/>
+      <c r="E2" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="12"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="12"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="12"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15" t="n">
+        <v>45017</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>194170.34574125</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <f aca="false">CapAc!H5+F6-E6</f>
+        <v>194170.34574125</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="15" t="n">
+        <v>45382</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" s="18" t="e">
+        <f aca="false">[2]InExp!E12</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H7" s="18" t="e">
+        <f aca="false">CapAc!H6+F7-E7</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="15" t="n">
+        <v>45382</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" s="18" t="e">
+        <f aca="false">[2]TDStoIT!F24</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H8" s="18" t="e">
+        <f aca="false">CapAc!H7+F8-E8</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="15" t="n">
+        <v>45382</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="E9" s="18" t="e">
+        <f aca="false">CapAc!H8</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H9" s="18" t="e">
+        <f aca="false">CapAc!H8+F9-E9</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="19"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="19"/>
+    </row>
+    <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="19"/>
+    </row>
+    <row r="15" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="21"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="21"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="9"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="9"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="15"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="9"/>
+    </row>
+    <row r="18" customFormat="false" ht="36.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="15"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="9"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="15"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="9"/>
+    </row>
+    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="15"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="9"/>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="15"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+    </row>
+    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="15"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="9"/>
+    </row>
+    <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="15"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+    </row>
+    <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="15"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="9"/>
+    </row>
+    <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="15"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="9"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="15"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="9"/>
+    </row>
+    <row r="27" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="15"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="9"/>
+    </row>
+    <row r="28" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="15"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+    </row>
+    <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="15"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="9"/>
+    </row>
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="15"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="9"/>
+    </row>
+    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="9"/>
+    </row>
+    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="24"/>
+    </row>
+    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:N39"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="17" width="14.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="10" width="14.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="18" width="14.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="17" width="14.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="17" width="24.33"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13" min="12" style="17" width="8.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="17" width="21.83"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="12"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="12"/>
+      <c r="E2" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15" t="n">
+        <v>45382</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <f aca="false">Bal!H5-F6+E6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="15"/>
+      <c r="C7" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="18" t="e">
+        <f aca="false">[2]BkAc!F7</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H7" s="18" t="e">
+        <f aca="false">Bal!H6-F7+E7</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="15"/>
+      <c r="C8" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="18" t="e">
+        <f aca="false">[2]CiH!F7</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H8" s="18" t="e">
+        <f aca="false">Bal!H7-F8+E8</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="15"/>
+      <c r="C9" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="18" t="e">
+        <f aca="false">[2]Inst!F10</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H9" s="18" t="e">
+        <f aca="false">Bal!H8-F9+E9</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="15" t="n">
+        <v>45382</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" s="18" t="e">
+        <f aca="false">[2]CapAc!E9</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H10" s="18" t="e">
+        <f aca="false">Bal!H9-F10+E10</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E11" s="18" t="e">
+        <f aca="false">SUM(E6:E10)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F11" s="18" t="e">
+        <f aca="false">SUM(F6:F10)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="12"/>
+      <c r="E15" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="19"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19"/>
+      <c r="B16" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="19"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="12"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="19"/>
+    </row>
+    <row r="18" customFormat="false" ht="36.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="28"/>
+      <c r="B18" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="30"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="34"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="9"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="9"/>
+    </row>
+    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="15" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="26" t="e">
+        <f aca="false">[2]CapAc!E9</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="H20" s="11"/>
+      <c r="I20" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="15" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="H21" s="11"/>
+      <c r="I21" s="9"/>
+    </row>
+    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="15" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="H22" s="11"/>
+      <c r="I22" s="9"/>
+    </row>
+    <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="15" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="I23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="18"/>
+    </row>
+    <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="15" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="I24" s="11" t="e">
+        <f aca="false">[2]BkAc!F7</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N24" s="11"/>
+    </row>
+    <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="15" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="I25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="18"/>
+      <c r="N25" s="18"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="15" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="I26" s="11" t="e">
+        <f aca="false">[2]CiH!F7</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N26" s="11"/>
+    </row>
+    <row r="27" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="15" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="H27" s="11"/>
+      <c r="I27" s="9"/>
+      <c r="N27" s="18"/>
+    </row>
+    <row r="28" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="15" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="I28" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="15" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I29" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="15" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="H30" s="11"/>
+      <c r="I30" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="15" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11" t="e">
+        <f aca="false">[2]Inst!F10</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K31" s="18"/>
+    </row>
+    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="15" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="H32" s="11"/>
+      <c r="I32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="18"/>
+    </row>
+    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="15" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="9"/>
+      <c r="K33" s="18"/>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="9"/>
+      <c r="N34" s="18"/>
+    </row>
+    <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="35"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D35" s="36" t="e">
+        <f aca="false">SUM(D20:D33)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E35" s="20"/>
+      <c r="F35" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" s="37"/>
+      <c r="H35" s="37"/>
+      <c r="I35" s="38" t="e">
+        <f aca="false">SUM(I20:I33)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N35" s="18"/>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N36" s="18"/>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>